--- a/entertainment_forms/002_podcast_guest_release_form--entertainment_forms.xlsx
+++ b/entertainment_forms/002_podcast_guest_release_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>guest_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>podcast_guest_release_form_1</t>
+          <t>Guest Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,248 +543,87 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>guest_name</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>published_on</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Published On</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Agreement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>publish</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>published_on</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>publish</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>published_on</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>agreement</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>agreement</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>agreement</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>agreement</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -803,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -849,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
@@ -866,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>i'm_not_sure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>I'm not sure</t>
         </is>
       </c>
     </row>
